--- a/StructureDefinition-openelis-organization.xlsx
+++ b/StructureDefinition-openelis-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3614" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3613" uniqueCount="568">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T02:24:20+00:00</t>
+    <t>2026-10-12T15:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -526,9 +526,6 @@
   </si>
   <si>
     <t>OpenELIS organization UUID</t>
-  </si>
-  <si>
-    <t>Currently only sent when the organization has a code (see Known Issues).</t>
   </si>
   <si>
     <t>Organization.fhirUuid</t>
@@ -3471,9 +3468,7 @@
       <c r="M12" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="N12" t="s" s="2">
-        <v>164</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
         <v>152</v>
       </c>
@@ -3539,7 +3534,7 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>157</v>
@@ -3556,10 +3551,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3582,13 +3577,13 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3639,28 +3634,28 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>79</v>
@@ -3671,10 +3666,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3703,7 +3698,7 @@
         <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>140</v>
@@ -3744,10 +3739,10 @@
         <v>79</v>
       </c>
       <c r="AB14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AC14" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>79</v>
@@ -3756,7 +3751,7 @@
         <v>155</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3777,7 +3772,7 @@
         <v>79</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>79</v>
@@ -3788,10 +3783,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3817,16 +3812,16 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3851,31 +3846,31 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3896,7 +3891,7 @@
         <v>134</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>79</v>
@@ -3907,10 +3902,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3933,19 +3928,19 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>79</v>
@@ -3970,31 +3965,31 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4012,10 +4007,10 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>79</v>
@@ -4026,10 +4021,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4055,16 +4050,16 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -4074,46 +4069,46 @@
         <v>79</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="T17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="T17" t="s" s="2">
+      <c r="U17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4131,13 +4126,13 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -4145,10 +4140,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4171,16 +4166,16 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4194,43 +4189,43 @@
         <v>79</v>
       </c>
       <c r="T18" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4248,13 +4243,13 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -4262,10 +4257,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4288,13 +4283,13 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4345,7 +4340,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4363,13 +4358,13 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4377,10 +4372,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4403,16 +4398,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4462,7 +4457,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4480,13 +4475,13 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4494,13 +4489,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>79</v>
@@ -4596,7 +4591,7 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>157</v>
@@ -4613,10 +4608,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4639,13 +4634,13 @@
         <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4696,28 +4691,28 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>79</v>
@@ -4728,10 +4723,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4760,7 +4755,7 @@
         <v>138</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>140</v>
@@ -4801,10 +4796,10 @@
         <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AC23" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>79</v>
@@ -4813,7 +4808,7 @@
         <v>155</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4834,7 +4829,7 @@
         <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>79</v>
@@ -4845,10 +4840,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4874,16 +4869,16 @@
         <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4908,31 +4903,31 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Z24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4953,7 +4948,7 @@
         <v>134</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4964,10 +4959,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4990,19 +4985,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -5027,31 +5022,31 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5069,10 +5064,10 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>79</v>
@@ -5083,10 +5078,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5112,16 +5107,16 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5131,46 +5126,46 @@
         <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5188,13 +5183,13 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -5202,10 +5197,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5228,16 +5223,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5251,43 +5246,43 @@
         <v>79</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5305,13 +5300,13 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5319,10 +5314,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5345,13 +5340,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5402,7 +5397,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5420,13 +5415,13 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5434,10 +5429,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5460,16 +5455,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5519,7 +5514,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5537,13 +5532,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5551,13 +5546,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>79</v>
@@ -5653,7 +5648,7 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>157</v>
@@ -5670,10 +5665,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5696,13 +5691,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5753,28 +5748,28 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>79</v>
@@ -5785,10 +5780,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5817,7 +5812,7 @@
         <v>138</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>140</v>
@@ -5858,10 +5853,10 @@
         <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AC32" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>79</v>
@@ -5870,7 +5865,7 @@
         <v>155</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5891,7 +5886,7 @@
         <v>79</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>79</v>
@@ -5902,10 +5897,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5931,16 +5926,16 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5965,31 +5960,31 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y33" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y33" t="s" s="2">
+      <c r="Z33" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6010,7 +6005,7 @@
         <v>134</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>79</v>
@@ -6021,10 +6016,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6047,19 +6042,19 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -6084,31 +6079,31 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y34" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y34" t="s" s="2">
+      <c r="Z34" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z34" t="s" s="2">
+      <c r="AA34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6126,10 +6121,10 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -6140,10 +6135,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6169,16 +6164,16 @@
         <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6188,46 +6183,46 @@
         <v>79</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T35" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6245,13 +6240,13 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
@@ -6259,10 +6254,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6285,16 +6280,16 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6308,43 +6303,43 @@
         <v>79</v>
       </c>
       <c r="T36" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6362,13 +6357,13 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6376,10 +6371,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6402,13 +6397,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6459,7 +6454,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6477,13 +6472,13 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6491,10 +6486,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6517,16 +6512,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6576,7 +6571,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6594,13 +6589,13 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6608,13 +6603,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -6710,7 +6705,7 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>157</v>
@@ -6727,10 +6722,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6753,13 +6748,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6810,28 +6805,28 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6842,10 +6837,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6874,7 +6869,7 @@
         <v>138</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>140</v>
@@ -6915,10 +6910,10 @@
         <v>79</v>
       </c>
       <c r="AB41" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AC41" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>79</v>
@@ -6927,7 +6922,7 @@
         <v>155</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6948,7 +6943,7 @@
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6959,10 +6954,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6988,16 +6983,16 @@
         <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7022,31 +7017,31 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y42" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7067,7 +7062,7 @@
         <v>134</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -7078,10 +7073,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7104,19 +7099,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -7141,31 +7136,31 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y43" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y43" t="s" s="2">
+      <c r="Z43" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AA43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7183,10 +7178,10 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -7197,10 +7192,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7226,16 +7221,16 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7245,46 +7240,46 @@
         <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T44" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7302,13 +7297,13 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7316,10 +7311,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7342,16 +7337,16 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7365,43 +7360,43 @@
         <v>79</v>
       </c>
       <c r="T45" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7419,13 +7414,13 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7433,10 +7428,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7459,13 +7454,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7516,7 +7511,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7534,13 +7529,13 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7548,10 +7543,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7574,16 +7569,16 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7633,7 +7628,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7651,13 +7646,13 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7665,13 +7660,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>79</v>
@@ -7696,13 +7691,13 @@
         <v>149</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M48" t="s" s="2">
         <v>151</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>152</v>
@@ -7786,10 +7781,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7812,13 +7807,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7869,28 +7864,28 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>79</v>
@@ -7901,10 +7896,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7933,7 +7928,7 @@
         <v>138</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>140</v>
@@ -7974,10 +7969,10 @@
         <v>79</v>
       </c>
       <c r="AB50" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AC50" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>79</v>
@@ -7986,7 +7981,7 @@
         <v>155</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8007,7 +8002,7 @@
         <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>79</v>
@@ -8018,10 +8013,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8047,16 +8042,16 @@
         <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8066,7 +8061,7 @@
         <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>79</v>
@@ -8081,31 +8076,31 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Z51" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Z51" t="s" s="2">
+      <c r="AA51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8126,7 +8121,7 @@
         <v>134</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>79</v>
@@ -8137,10 +8132,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8163,19 +8158,19 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8200,31 +8195,31 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y52" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y52" t="s" s="2">
+      <c r="Z52" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z52" t="s" s="2">
+      <c r="AA52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8242,10 +8237,10 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
@@ -8256,10 +8251,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8285,16 +8280,16 @@
         <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8304,46 +8299,46 @@
         <v>79</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T53" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8361,13 +8356,13 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8375,10 +8370,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8401,16 +8396,16 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8424,43 +8419,43 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8478,13 +8473,13 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8492,10 +8487,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8518,13 +8513,13 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8575,7 +8570,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8593,13 +8588,13 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8607,10 +8602,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8633,16 +8628,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L56" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="M56" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8692,7 +8687,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8710,13 +8705,13 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8724,10 +8719,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8750,26 +8745,26 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="O57" t="s" s="2">
+      <c r="P57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q57" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="P57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q57" t="s" s="2">
-        <v>301</v>
-      </c>
       <c r="R57" t="s" s="2">
         <v>79</v>
       </c>
@@ -8813,7 +8808,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8828,27 +8823,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8871,19 +8866,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -8908,14 +8903,14 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="Y58" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="Y58" t="s" s="2">
+      <c r="Z58" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>314</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8932,7 +8927,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8947,27 +8942,27 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>318</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8990,13 +8985,13 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9047,28 +9042,28 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>79</v>
@@ -9079,10 +9074,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9111,7 +9106,7 @@
         <v>138</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>140</v>
@@ -9152,10 +9147,10 @@
         <v>79</v>
       </c>
       <c r="AB60" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AC60" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>79</v>
@@ -9164,7 +9159,7 @@
         <v>155</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9185,7 +9180,7 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>79</v>
@@ -9196,10 +9191,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9222,19 +9217,19 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9281,7 +9276,7 @@
         <v>155</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9299,10 +9294,10 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>79</v>
@@ -9313,13 +9308,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>79</v>
@@ -9341,19 +9336,19 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -9402,7 +9397,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9420,10 +9415,10 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>79</v>
@@ -9434,10 +9429,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9460,13 +9455,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9517,28 +9512,28 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>79</v>
@@ -9549,10 +9544,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9581,7 +9576,7 @@
         <v>138</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>140</v>
@@ -9622,10 +9617,10 @@
         <v>79</v>
       </c>
       <c r="AB64" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AC64" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>79</v>
@@ -9634,7 +9629,7 @@
         <v>155</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9655,7 +9650,7 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>79</v>
@@ -9666,10 +9661,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9695,16 +9690,16 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9714,46 +9709,46 @@
         <v>79</v>
       </c>
       <c r="S65" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9771,10 +9766,10 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>79</v>
@@ -9785,10 +9780,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9811,16 +9806,16 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9870,7 +9865,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9888,10 +9883,10 @@
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>79</v>
@@ -9902,10 +9897,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9931,14 +9926,14 @@
         <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -9987,7 +9982,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10005,10 +10000,10 @@
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>79</v>
@@ -10019,10 +10014,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10045,17 +10040,17 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10104,7 +10099,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10122,10 +10117,10 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>79</v>
@@ -10136,10 +10131,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10162,19 +10157,19 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10223,7 +10218,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10241,10 +10236,10 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>79</v>
@@ -10255,10 +10250,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10281,19 +10276,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -10342,7 +10337,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10360,10 +10355,10 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>79</v>
@@ -10374,10 +10369,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10400,19 +10395,19 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10461,7 +10456,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10476,16 +10471,16 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AM71" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10493,10 +10488,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10519,19 +10514,19 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10580,7 +10575,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10601,7 +10596,7 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>79</v>
@@ -10612,10 +10607,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10638,19 +10633,19 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10699,7 +10694,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10708,22 +10703,22 @@
         <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AJ73" t="s" s="2">
+      <c r="AK73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AK73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL73" t="s" s="2">
+      <c r="AM73" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10731,10 +10726,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10757,19 +10752,19 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10818,7 +10813,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10827,22 +10822,22 @@
         <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AJ74" t="s" s="2">
+      <c r="AK74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AK74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AM74" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -10850,10 +10845,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10876,13 +10871,13 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10933,28 +10928,28 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>79</v>
@@ -10965,10 +10960,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10997,7 +10992,7 @@
         <v>138</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>140</v>
@@ -11038,10 +11033,10 @@
         <v>79</v>
       </c>
       <c r="AB76" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AC76" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>79</v>
@@ -11050,7 +11045,7 @@
         <v>155</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11071,7 +11066,7 @@
         <v>79</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>79</v>
@@ -11082,10 +11077,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11111,16 +11106,16 @@
         <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>79</v>
@@ -11133,43 +11128,43 @@
         <v>79</v>
       </c>
       <c r="T77" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y77" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="U77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y77" t="s" s="2">
+      <c r="Z77" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="Z77" t="s" s="2">
+      <c r="AA77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11187,13 +11182,13 @@
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>79</v>
@@ -11201,10 +11196,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11230,13 +11225,13 @@
         <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11250,43 +11245,43 @@
         <v>79</v>
       </c>
       <c r="T78" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y78" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="U78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y78" t="s" s="2">
+      <c r="Z78" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="Z78" t="s" s="2">
+      <c r="AA78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11304,10 +11299,10 @@
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>79</v>
@@ -11318,10 +11313,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11344,19 +11339,19 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11369,43 +11364,43 @@
         <v>79</v>
       </c>
       <c r="T79" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11423,10 +11418,10 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>79</v>
@@ -11437,10 +11432,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11463,13 +11458,13 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11484,43 +11479,43 @@
         <v>79</v>
       </c>
       <c r="T80" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11535,16 +11530,16 @@
         <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL80" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AL80" t="s" s="2">
+      <c r="AM80" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AM80" t="s" s="2">
+      <c r="AN80" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -11552,14 +11547,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11578,13 +11573,13 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11599,43 +11594,43 @@
         <v>79</v>
       </c>
       <c r="T81" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11650,16 +11645,16 @@
         <v>103</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL81" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AL81" t="s" s="2">
+      <c r="AM81" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -11667,14 +11662,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11693,16 +11688,16 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11716,43 +11711,43 @@
         <v>79</v>
       </c>
       <c r="T82" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11770,10 +11765,10 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>79</v>
@@ -11784,14 +11779,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11810,13 +11805,13 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11867,7 +11862,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -11882,16 +11877,16 @@
         <v>103</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AL83" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AL83" t="s" s="2">
+      <c r="AM83" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -11899,14 +11894,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11925,13 +11920,13 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11946,43 +11941,43 @@
         <v>79</v>
       </c>
       <c r="T84" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -11997,16 +11992,16 @@
         <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AL84" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AL84" t="s" s="2">
+      <c r="AM84" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>79</v>
@@ -12014,10 +12009,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12040,16 +12035,16 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12099,7 +12094,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12117,13 +12112,13 @@
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AN85" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>79</v>
@@ -12131,10 +12126,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12157,17 +12152,17 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -12180,43 +12175,43 @@
         <v>79</v>
       </c>
       <c r="T86" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12234,13 +12229,13 @@
         <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="AM86" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="AN86" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>79</v>
@@ -12248,10 +12243,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12274,17 +12269,17 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -12333,7 +12328,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12348,16 +12343,16 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AL87" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="AN87" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12365,10 +12360,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12391,19 +12386,19 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -12452,7 +12447,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12473,7 +12468,7 @@
         <v>79</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>79</v>
@@ -12484,10 +12479,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12510,13 +12505,13 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12567,28 +12562,28 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>79</v>
@@ -12599,10 +12594,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12631,7 +12626,7 @@
         <v>138</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>140</v>
@@ -12684,7 +12679,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12705,7 +12700,7 @@
         <v>79</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>79</v>
@@ -12716,14 +12711,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12745,10 +12740,10 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>140</v>
@@ -12803,7 +12798,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12835,10 +12830,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12861,17 +12856,17 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -12896,14 +12891,14 @@
         <v>79</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>543</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
       </c>
@@ -12920,7 +12915,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -12941,7 +12936,7 @@
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>79</v>
@@ -12952,10 +12947,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12978,17 +12973,17 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -13037,7 +13032,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13055,10 +13050,10 @@
         <v>79</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>79</v>
@@ -13069,10 +13064,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13095,17 +13090,17 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>79</v>
@@ -13154,7 +13149,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13172,10 +13167,10 @@
         <v>79</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>79</v>
@@ -13186,10 +13181,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13212,17 +13207,17 @@
         <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>79</v>
@@ -13271,7 +13266,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13289,10 +13284,10 @@
         <v>79</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>79</v>
@@ -13303,10 +13298,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13329,17 +13324,17 @@
         <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>79</v>
@@ -13388,7 +13383,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13409,7 +13404,7 @@
         <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>79</v>

--- a/StructureDefinition-openelis-organization.xlsx
+++ b/StructureDefinition-openelis-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:07:11+00:00</t>
+    <t>2026-10-12T15:22:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-organization.xlsx
+++ b/StructureDefinition-openelis-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:22:52+00:00</t>
+    <t>2026-10-14T21:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
